--- a/bjt-front/bjt-product-system/generated_sql_imports/machine.xlsx
+++ b/bjt-front/bjt-product-system/generated_sql_imports/machine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17260" activeTab="2"/>
+    <workbookView windowHeight="17260" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="型号表" sheetId="1" r:id="rId1"/>
@@ -10292,7 +10292,7 @@
       <c r="X2" s="5"/>
       <c r="Y2" s="5"/>
     </row>
-    <row r="3" ht="27.75" customHeight="1" spans="1:25">
+    <row r="3" ht="98" customHeight="1" spans="1:25">
       <c r="A3" s="5" t="s">
         <v>73</v>
       </c>
@@ -11385,7 +11385,7 @@
       <c r="Z2" s="157"/>
       <c r="AA2" s="157"/>
     </row>
-    <row r="3" ht="32" customHeight="1" spans="1:27">
+    <row r="3" ht="84" customHeight="1" spans="1:27">
       <c r="A3" s="5" t="s">
         <v>73</v>
       </c>
@@ -12330,7 +12330,10 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:53">
-      <c r="A1" s="127"/>
+      <c r="A1" s="127" t="e">
+        <f>-A7</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="B1" s="127"/>
       <c r="C1" s="127"/>
       <c r="D1" s="127"/>
@@ -14898,7 +14901,7 @@
       </c>
       <c r="S6" s="9"/>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:19">
+    <row r="7" ht="67" customHeight="1" spans="1:19">
       <c r="A7" s="19" t="s">
         <v>81</v>
       </c>
@@ -14976,7 +14979,7 @@
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
     </row>
-    <row r="9" ht="20" customHeight="1" spans="1:19">
+    <row r="9" ht="49" customHeight="1" spans="1:19">
       <c r="A9" s="19" t="s">
         <v>83</v>
       </c>
